--- a/Excel/11_Wastewater_WIP_v02.xlsx
+++ b/Excel/11_Wastewater_WIP_v02.xlsx
@@ -751,9 +751,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>←</t>
@@ -761,9 +761,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve"> Please select</t>
@@ -776,9 +776,9 @@
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>E</t>
@@ -787,9 +787,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>CH4</t>
@@ -802,9 +802,9 @@
     <r>
       <rPr>
         <vertAlign val="subscript"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>CO2e</t>
@@ -1003,108 +1003,106 @@
   </numFmts>
   <fonts count="53" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1115,248 +1113,242 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="18"/>
+      <color theme="3" tint="9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <vertAlign val="subscript"/>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <i/>
+      <vertAlign val="subscript"/>
       <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="subscript"/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -2307,11 +2299,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2331,11 +2322,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2355,11 +2345,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2379,11 +2368,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2403,11 +2391,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2427,11 +2414,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2451,11 +2437,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2475,11 +2460,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2499,11 +2483,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2523,11 +2506,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2547,11 +2529,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2571,11 +2552,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2595,11 +2575,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2619,11 +2598,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2643,11 +2621,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2667,11 +2644,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2691,11 +2667,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2715,11 +2690,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2739,11 +2713,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2763,11 +2736,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2787,11 +2759,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2811,11 +2782,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2835,11 +2805,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2859,11 +2828,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2883,11 +2851,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2907,11 +2874,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2931,11 +2897,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2955,11 +2920,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2979,11 +2943,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3003,11 +2966,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3027,11 +2989,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3051,11 +3012,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3075,11 +3035,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3099,11 +3058,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3123,11 +3081,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3147,11 +3104,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3171,11 +3127,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3195,11 +3150,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3219,11 +3173,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3243,11 +3196,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3267,11 +3219,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3291,11 +3242,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3315,11 +3265,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3625,7 +3574,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -3699,17 +3648,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{B377A225-5B38-4F4F-8E60-34C9F7D0C552}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Methane emissions from wastewater treatment</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3770,7 +3719,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -3844,17 +3793,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{C591D420-5510-4F7D-A38B-480C54C6057C}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Nitrous oxide emissions from flared biogas</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -4152,14 +4101,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4167,13 +4116,13 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐶𝐻</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>4</m:t>
@@ -4181,7 +4130,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4189,14 +4138,14 @@
                     <m:f>
                       <m:fPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:fPr>
                       <m:num>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>1</m:t>
@@ -4204,7 +4153,7 @@
                       </m:num>
                       <m:den>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>1000</m:t>
@@ -4212,7 +4161,7 @@
                       </m:den>
                     </m:f>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -4222,7 +4171,7 @@
                         <m:begChr m:val="{"/>
                         <m:endChr m:val="}"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -4233,7 +4182,7 @@
                             <m:begChr m:val="{"/>
                             <m:endChr m:val="}"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -4242,14 +4191,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑊</m:t>
@@ -4257,7 +4206,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑡</m:t>
@@ -4265,7 +4214,7 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -4275,14 +4224,14 @@
                                 <m:begChr m:val="["/>
                                 <m:endChr m:val="]"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝑂</m:t>
@@ -4290,14 +4239,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐷</m:t>
@@ -4305,7 +4254,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑖𝑛</m:t>
@@ -4313,7 +4262,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>×</m:t>
@@ -4321,14 +4270,14 @@
                                 <m:d>
                                   <m:dPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:dPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>1−</m:t>
@@ -4336,14 +4285,14 @@
                                     <m:sSub>
                                       <m:sSubPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
                                       </m:sSubPr>
                                       <m:e>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝐹</m:t>
@@ -4351,7 +4300,7 @@
                                       </m:e>
                                       <m:sub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑠𝑙𝑢𝑑𝑔𝑒</m:t>
@@ -4361,13 +4310,13 @@
                                   </m:e>
                                 </m:d>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>−</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝑂</m:t>
@@ -4375,14 +4324,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐷</m:t>
@@ -4390,7 +4339,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜𝑢𝑡</m:t>
@@ -4400,13 +4349,13 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐶</m:t>
@@ -4414,14 +4363,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐹</m:t>
@@ -4429,19 +4378,19 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑤𝑤</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>,</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑡</m:t>
@@ -4449,13 +4398,13 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐸</m:t>
@@ -4463,14 +4412,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐹</m:t>
@@ -4478,7 +4427,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑤𝑤</m:t>
@@ -4488,7 +4437,7 @@
                           </m:e>
                         </m:d>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>+</m:t>
@@ -4498,7 +4447,7 @@
                             <m:begChr m:val="{"/>
                             <m:endChr m:val="}"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -4507,14 +4456,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑊</m:t>
@@ -4522,7 +4471,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑡</m:t>
@@ -4530,7 +4479,7 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -4540,14 +4489,14 @@
                                 <m:begChr m:val="["/>
                                 <m:endChr m:val="]"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐶𝑂</m:t>
@@ -4555,14 +4504,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐷</m:t>
@@ -4570,7 +4519,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑖𝑛</m:t>
@@ -4578,7 +4527,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>×</m:t>
@@ -4586,7 +4535,7 @@
                                 <m:d>
                                   <m:dPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
@@ -4595,14 +4544,14 @@
                                     <m:sSub>
                                       <m:sSubPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
                                       </m:sSubPr>
                                       <m:e>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝐹</m:t>
@@ -4610,7 +4559,7 @@
                                       </m:e>
                                       <m:sub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑠𝑙𝑢𝑑𝑔𝑒</m:t>
@@ -4618,7 +4567,7 @@
                                       </m:sub>
                                     </m:sSub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>−</m:t>
@@ -4626,14 +4575,14 @@
                                     <m:sSub>
                                       <m:sSubPr>
                                         <m:ctrlPr>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                         </m:ctrlPr>
                                       </m:sSubPr>
                                       <m:e>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝐹</m:t>
@@ -4641,7 +4590,7 @@
                                       </m:e>
                                       <m:sub>
                                         <m:r>
-                                          <a:rPr lang="en-AU" sz="1100" i="1">
+                                          <a:rPr lang="en-AU" sz="1000" i="1">
                                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                           </a:rPr>
                                           <m:t>𝑟𝑒𝑚𝑜𝑣𝑒𝑑</m:t>
@@ -4653,13 +4602,13 @@
                               </m:e>
                             </m:d>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐶</m:t>
@@ -4667,14 +4616,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐹</m:t>
@@ -4682,19 +4631,19 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑠𝑙𝑢𝑑𝑔𝑒</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>,</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑡</m:t>
@@ -4702,13 +4651,13 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐸</m:t>
@@ -4716,14 +4665,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐹</m:t>
@@ -4731,7 +4680,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑠𝑙𝑢𝑑𝑔𝑒</m:t>
@@ -4741,7 +4690,7 @@
                           </m:e>
                         </m:d>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>−</m:t>
@@ -4751,14 +4700,14 @@
                             <m:begChr m:val="{"/>
                             <m:endChr m:val="}"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:dPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>6.784×</m:t>
@@ -4766,14 +4715,14 @@
                             <m:sSup>
                               <m:sSupPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSupPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>10</m:t>
@@ -4781,7 +4730,7 @@
                               </m:e>
                               <m:sup>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>−4</m:t>
@@ -4789,7 +4738,7 @@
                               </m:sup>
                             </m:sSup>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -4799,7 +4748,7 @@
                                 <m:begChr m:val="["/>
                                 <m:endChr m:val="]"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
@@ -4808,14 +4757,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑄</m:t>
@@ -4823,7 +4772,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑐𝑎𝑝</m:t>
@@ -4831,7 +4780,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>+</m:t>
@@ -4839,14 +4788,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑄</m:t>
@@ -4854,7 +4803,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
@@ -4862,7 +4811,7 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>+</m:t>
@@ -4870,14 +4819,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑄</m:t>
@@ -4885,7 +4834,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑜𝑢𝑡</m:t>
@@ -4897,7 +4846,7 @@
                           </m:e>
                         </m:d>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>+</m:t>
@@ -4907,7 +4856,7 @@
                             <m:begChr m:val="{"/>
                             <m:endChr m:val="}"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -4916,14 +4865,14 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:sSubPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑄</m:t>
@@ -4931,7 +4880,7 @@
                               </m:e>
                               <m:sub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
@@ -4939,7 +4888,7 @@
                               </m:sub>
                             </m:sSub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>×</m:t>
@@ -4949,14 +4898,14 @@
                                 <m:begChr m:val="["/>
                                 <m:endChr m:val="]"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
                               </m:dPr>
                               <m:e>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐸</m:t>
@@ -4964,14 +4913,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐶</m:t>
@@ -4979,7 +4928,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
@@ -4987,13 +4936,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐸</m:t>
@@ -5001,14 +4950,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐹</m:t>
@@ -5016,25 +4965,25 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
                                     </m:r>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>,</m:t>
                                     </m:r>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐶𝐻</m:t>
                                     </m:r>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>4</m:t>
@@ -5050,7 +4999,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5099,7 +5048,7 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝐶𝐻4=1/1000×{{𝑊_𝑡×[𝐶𝑂𝐷_𝑖𝑛×(1−𝐹_𝑠𝑙𝑢𝑑𝑔𝑒 )−𝐶𝑂𝐷_𝑜𝑢𝑡 ]×𝐶𝐹_(𝑤𝑤,𝑡)×𝐸𝐹_𝑤𝑤 }+{𝑊_𝑡×[𝐶𝑂𝐷_𝑖𝑛×(𝐹_𝑠𝑙𝑢𝑑𝑔𝑒−𝐹_𝑟𝑒𝑚𝑜𝑣𝑒𝑑 )]×𝐶𝐹_(𝑠𝑙𝑢𝑑𝑔𝑒,𝑡)×𝐸𝐹_𝑠𝑙𝑢𝑑𝑔𝑒 }−{6.784×10^(−4)×[𝑄_𝑐𝑎𝑝+𝑄_𝑓𝑙𝑎𝑟𝑒𝑑+𝑄_𝑜𝑢𝑡 ]}+{𝑄_𝑓𝑙𝑎𝑟𝑒𝑑×[𝐸𝐶_𝑓𝑙𝑎𝑟𝑒𝑑×𝐸𝐹_(𝑓𝑙𝑎𝑟𝑒𝑑,𝐶𝐻4) ]}}</a:t>
@@ -5174,14 +5123,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -5189,19 +5138,19 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑁</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>2</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑂</m:t>
@@ -5209,7 +5158,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -5217,7 +5166,7 @@
                     <m:f>
                       <m:fPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -5226,14 +5175,14 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑄</m:t>
@@ -5241,7 +5190,7 @@
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
@@ -5251,7 +5200,7 @@
                       </m:num>
                       <m:den>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>1000</m:t>
@@ -5259,7 +5208,7 @@
                       </m:den>
                     </m:f>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
@@ -5269,14 +5218,14 @@
                         <m:begChr m:val="["/>
                         <m:endChr m:val="]"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:dPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -5284,14 +5233,14 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐶</m:t>
@@ -5299,7 +5248,7 @@
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
@@ -5307,13 +5256,13 @@
                           </m:sub>
                         </m:sSub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>×</m:t>
                         </m:r>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -5321,14 +5270,14 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝐹</m:t>
@@ -5336,31 +5285,31 @@
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑓𝑙𝑎𝑟𝑒𝑑</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>,</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑁</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>2</m:t>
                             </m:r>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑂</m:t>
@@ -5372,7 +5321,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5421,7 +5370,7 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝑁2𝑂=𝑄_𝑓𝑙𝑎𝑟𝑒𝑑/1000×[𝐸𝐶_𝑓𝑙𝑎𝑟𝑒𝑑×𝐸𝐹_(𝑓𝑙𝑎𝑟𝑒𝑑,𝑁2𝑂) ]</a:t>
@@ -6101,12 +6050,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -6317,31 +6266,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="75" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -6358,7 +6307,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:W45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -6388,7 +6337,7 @@
       <c r="O1" s="49"/>
       <c r="P1" s="49"/>
     </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
       <c r="E2" s="49"/>
@@ -6405,7 +6354,7 @@
       <c r="P2" s="49"/>
       <c r="Q2" s="50"/>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6425,13 +6374,13 @@
       <c r="O3" s="51"/>
       <c r="P3" s="51"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6451,7 +6400,7 @@
       <c r="N5" s="34"/>
       <c r="O5" s="31"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="52" t="s">
         <v>83</v>
       </c>
@@ -6467,32 +6416,32 @@
       <c r="N6" s="33"/>
       <c r="O6" s="32"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
         <v>Wastewater</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
         <v>11.1.1-2 Wastewater CH4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="str">
         <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
         <v>11.1.3-4 Wastewater N2O</v>
@@ -6501,53 +6450,53 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
         <v>Constants - Wastewater</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="12:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:23" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="W45" t="s">
         <v>81</v>
       </c>
@@ -6565,7 +6514,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -6583,10 +6532,10 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6601,7 +6550,7 @@
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -6618,7 +6567,7 @@
       <c r="J4" s="17"/>
       <c r="K4" s="18"/>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6633,7 +6582,7 @@
       <c r="J5" s="20"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="16"/>
       <c r="D6" s="15" t="s">
         <v>79</v>
@@ -6646,7 +6595,7 @@
       <c r="J6" s="16"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -6657,7 +6606,7 @@
       <c r="J7" s="16"/>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -6685,7 +6634,7 @@
       </c>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
         <v>Wastewater</v>
@@ -6718,7 +6667,7 @@
       </c>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="16"/>
       <c r="D10" s="1" t="s">
         <v>124</v>
@@ -6747,7 +6696,7 @@
       </c>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="16"/>
       <c r="D11" s="71" t="s">
         <v>130</v>
@@ -6768,7 +6717,7 @@
       </c>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -6782,7 +6731,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
         <v>11.1.1-2 Wastewater CH4</v>
@@ -6797,7 +6746,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="16"/>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="str">
         <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
         <v>11.1.3-4 Wastewater N2O</v>
@@ -6812,7 +6761,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="16"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -6823,7 +6772,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="16"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -6834,7 +6783,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="s">
         <v>1</v>
       </c>
@@ -6848,7 +6797,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
         <v>Constants - Wastewater</v>
@@ -6863,7 +6812,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -6878,7 +6827,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="16"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -6889,7 +6838,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="16"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -6900,7 +6849,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="16"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -6911,7 +6860,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="16"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -6922,7 +6871,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="16"/>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="16"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -6933,7 +6882,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="16"/>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="16"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -6944,7 +6893,7 @@
       <c r="J25" s="1"/>
       <c r="K25" s="16"/>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="16"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -6955,7 +6904,7 @@
       <c r="J26" s="1"/>
       <c r="K26" s="16"/>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="16"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6966,7 +6915,7 @@
       <c r="J27" s="1"/>
       <c r="K27" s="16"/>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="16"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -6977,7 +6926,7 @@
       <c r="J28" s="1"/>
       <c r="K28" s="16"/>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="16"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -6988,7 +6937,7 @@
       <c r="J29" s="1"/>
       <c r="K29" s="16"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="16"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -6999,7 +6948,7 @@
       <c r="J30" s="1"/>
       <c r="K30" s="16"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="16"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -7010,7 +6959,7 @@
       <c r="J31" s="1"/>
       <c r="K31" s="16"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="16"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -7021,7 +6970,7 @@
       <c r="J32" s="1"/>
       <c r="K32" s="16"/>
     </row>
-    <row r="33" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="16"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -7032,7 +6981,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="16"/>
     </row>
-    <row r="34" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="16"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -7043,7 +6992,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="16"/>
     </row>
-    <row r="35" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="16"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -7054,7 +7003,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="16"/>
     </row>
-    <row r="36" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="16"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -7065,7 +7014,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="16"/>
     </row>
-    <row r="37" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="16"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -7076,7 +7025,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="16"/>
     </row>
-    <row r="38" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="16"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -7087,7 +7036,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="16"/>
     </row>
-    <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="16"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -7098,7 +7047,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="16"/>
     </row>
-    <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -7109,7 +7058,7 @@
       <c r="J40" s="1"/>
       <c r="K40" s="16"/>
     </row>
-    <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="16"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -7120,7 +7069,7 @@
       <c r="J41" s="1"/>
       <c r="K41" s="16"/>
     </row>
-    <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="16"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -7131,7 +7080,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="16"/>
     </row>
-    <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="16"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -7142,7 +7091,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="16"/>
     </row>
-    <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="16"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -7153,7 +7102,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="16"/>
     </row>
-    <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="16"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -7164,7 +7113,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="16"/>
     </row>
-    <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="16"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -7175,7 +7124,7 @@
       <c r="J46" s="1"/>
       <c r="K46" s="16"/>
     </row>
-    <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="16"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -7186,7 +7135,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="16"/>
     </row>
-    <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="16"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -7197,7 +7146,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="16"/>
     </row>
-    <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="16"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -7208,7 +7157,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="16"/>
     </row>
-    <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="16"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -7219,7 +7168,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="16"/>
     </row>
-    <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="16"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -7230,7 +7179,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="16"/>
     </row>
-    <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="16"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -7241,7 +7190,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="16"/>
     </row>
-    <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="16"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -7252,7 +7201,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="16"/>
     </row>
-    <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="16"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -7263,7 +7212,7 @@
       <c r="J54" s="1"/>
       <c r="K54" s="16"/>
     </row>
-    <row r="55" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="16"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -7274,7 +7223,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="16"/>
     </row>
-    <row r="56" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="16"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -7285,7 +7234,7 @@
       <c r="J56" s="1"/>
       <c r="K56" s="16"/>
     </row>
-    <row r="57" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="16"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -7296,7 +7245,7 @@
       <c r="J57" s="1"/>
       <c r="K57" s="16"/>
     </row>
-    <row r="58" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="16"/>
       <c r="D58" s="1"/>
       <c r="E58" s="22"/>
@@ -7307,7 +7256,7 @@
       <c r="J58" s="16"/>
       <c r="K58" s="16"/>
     </row>
-    <row r="59" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="16"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -7318,7 +7267,7 @@
       <c r="J59" s="1"/>
       <c r="K59" s="16"/>
     </row>
-    <row r="60" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="16"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -7329,7 +7278,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="16"/>
     </row>
-    <row r="61" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="16"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -7340,7 +7289,7 @@
       <c r="J61" s="1"/>
       <c r="K61" s="16"/>
     </row>
-    <row r="62" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="16"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -7351,7 +7300,7 @@
       <c r="J62" s="1"/>
       <c r="K62" s="16"/>
     </row>
-    <row r="63" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="16"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -7362,7 +7311,7 @@
       <c r="J63" s="1"/>
       <c r="K63" s="16"/>
     </row>
-    <row r="64" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="16"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -7373,7 +7322,7 @@
       <c r="J64" s="1"/>
       <c r="K64" s="16"/>
     </row>
-    <row r="65" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="16"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -7384,7 +7333,7 @@
       <c r="J65" s="1"/>
       <c r="K65" s="16"/>
     </row>
-    <row r="66" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="16"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -7395,7 +7344,7 @@
       <c r="J66" s="1"/>
       <c r="K66" s="16"/>
     </row>
-    <row r="67" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="16"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -7406,7 +7355,7 @@
       <c r="J67" s="1"/>
       <c r="K67" s="16"/>
     </row>
-    <row r="68" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="16"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -7417,7 +7366,7 @@
       <c r="J68" s="1"/>
       <c r="K68" s="16"/>
     </row>
-    <row r="69" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="16"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -7428,7 +7377,7 @@
       <c r="J69" s="1"/>
       <c r="K69" s="16"/>
     </row>
-    <row r="70" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="16"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -7439,7 +7388,7 @@
       <c r="J70" s="1"/>
       <c r="K70" s="16"/>
     </row>
-    <row r="71" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="16"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -7450,7 +7399,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="16"/>
     </row>
-    <row r="72" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="16"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -7461,7 +7410,7 @@
       <c r="J72" s="1"/>
       <c r="K72" s="16"/>
     </row>
-    <row r="73" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="16"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -7472,7 +7421,7 @@
       <c r="J73" s="1"/>
       <c r="K73" s="16"/>
     </row>
-    <row r="74" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="16"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -7483,7 +7432,7 @@
       <c r="J74" s="1"/>
       <c r="K74" s="16"/>
     </row>
-    <row r="75" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="16"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -7494,7 +7443,7 @@
       <c r="J75" s="1"/>
       <c r="K75" s="16"/>
     </row>
-    <row r="76" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="16"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -7505,7 +7454,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="16"/>
     </row>
-    <row r="77" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="16"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -7516,7 +7465,7 @@
       <c r="J77" s="1"/>
       <c r="K77" s="16"/>
     </row>
-    <row r="78" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="16"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -7527,7 +7476,7 @@
       <c r="J78" s="1"/>
       <c r="K78" s="16"/>
     </row>
-    <row r="79" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="16"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -7538,7 +7487,7 @@
       <c r="J79" s="1"/>
       <c r="K79" s="16"/>
     </row>
-    <row r="80" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="16"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -7549,7 +7498,7 @@
       <c r="J80" s="1"/>
       <c r="K80" s="16"/>
     </row>
-    <row r="81" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="16"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -7560,7 +7509,7 @@
       <c r="J81" s="1"/>
       <c r="K81" s="16"/>
     </row>
-    <row r="82" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="16"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -7571,7 +7520,7 @@
       <c r="J82" s="1"/>
       <c r="K82" s="16"/>
     </row>
-    <row r="83" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="16"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -7582,7 +7531,7 @@
       <c r="J83" s="1"/>
       <c r="K83" s="16"/>
     </row>
-    <row r="84" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="16"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -7593,7 +7542,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="16"/>
     </row>
-    <row r="85" spans="3:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="16"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -7604,7 +7553,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="16"/>
     </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
@@ -7615,7 +7564,7 @@
       <c r="J86" s="16"/>
       <c r="K86" s="16"/>
     </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
       <c r="E87" s="16"/>
@@ -7637,7 +7586,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:L371"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -7660,10 +7609,10 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -7677,13 +7626,13 @@
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -7692,8 +7641,8 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="s">
         <v>116</v>
       </c>
@@ -7704,7 +7653,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -7718,19 +7667,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="str">
         <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
         <v>Wastewater</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="64" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -7740,13 +7689,13 @@
       <c r="E12" s="63"/>
       <c r="F12" s="55"/>
     </row>
-    <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
         <v>11.1.1-2 Wastewater CH4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="str">
         <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
         <v>11.1.3-4 Wastewater N2O</v>
@@ -7761,7 +7710,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="1" t="s">
         <v>101</v>
       </c>
@@ -7772,7 +7721,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="1" t="s">
         <v>113</v>
       </c>
@@ -7783,7 +7732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="s">
         <v>1</v>
       </c>
@@ -7797,33 +7746,33 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
         <v>Constants - Wastewater</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="64" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="54" t="s">
         <v>111</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="55"/>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
         <v>96</v>
       </c>
@@ -7834,7 +7783,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>97</v>
       </c>
@@ -7845,7 +7794,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
         <v>98</v>
       </c>
@@ -7856,41 +7805,41 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K29" s="43"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K30" s="43"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K32" s="43"/>
     </row>
-    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K33" s="43"/>
     </row>
-    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K34" s="43"/>
     </row>
-    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L36" s="43"/>
     </row>
-    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="43"/>
     </row>
-    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="42"/>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="42"/>
       <c r="J39" s="42"/>
     </row>
-    <row r="40" spans="1:12" s="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="43" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -7901,7 +7850,7 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:12" s="43" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="43" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -7915,59 +7864,59 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E55" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="1">
         <f>X_Cell_Wastewater_QuantityInM3*(X_Cell_Wastewater_InletCOD*(1-X_Cell_Wastewater_FractionCODRemovedAsSludge)-X_Cell_Wastewater_OutletCOD)</f>
         <v>350</v>
       </c>
     </row>
-    <row r="58" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E59" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="61" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1" t="s">
         <v>106</v>
       </c>
@@ -7975,115 +7924,115 @@
         <v>108</v>
       </c>
     </row>
-    <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" spans="4:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D371" s="35"/>
     </row>
   </sheetData>
@@ -8201,7 +8150,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:L342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -8219,10 +8168,10 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -8240,13 +8189,13 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -8256,19 +8205,19 @@
         <v>Methane emissions from wastewater treatment</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Source()</f>
         <v>VEERG 2026: 11.1.1.1, Equation (1)</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="29" t="str" cm="1">
         <f t="array" ref="D7">Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment_Variation()</f>
         <v xml:space="preserve">VARIATION ON SOURCE: Changed units of EF_ww, EF_Sludge and EF_flared from CO2e to CH4 to match data in Table </v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -8280,14 +8229,14 @@
         <v>=Wastewater_Methane_Equations.VEERG_11_1_1_1__1_MethaneEmissionsFromWastewaterTreatment</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
         <v>Wastewater</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="27" t="s">
         <v>12</v>
       </c>
@@ -8296,7 +8245,7 @@
         <v>E_CH4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -8308,13 +8257,13 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="str">
         <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
         <v>11.1.1-2 Wastewater CH4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="str">
         <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
         <v>11.1.3-4 Wastewater N2O</v>
@@ -8340,7 +8289,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="44" t="str">
         <v>COD_in</v>
       </c>
@@ -8360,7 +8309,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="44" t="str">
         <v>F_sludge</v>
       </c>
@@ -8380,7 +8329,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="s">
         <v>1</v>
       </c>
@@ -8403,7 +8352,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
         <v>Constants - Wastewater</v>
@@ -8427,7 +8376,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -8451,7 +8400,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="44" t="str">
         <v>F_removed</v>
       </c>
@@ -8471,7 +8420,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="44" t="str">
         <v>CF_sludge_t</v>
       </c>
@@ -8491,7 +8440,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="44" t="str">
         <v>EF_sludge</v>
       </c>
@@ -8511,7 +8460,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="44" t="str">
         <v>Q_cap</v>
       </c>
@@ -8531,7 +8480,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="44" t="str">
         <v>Q_flared</v>
       </c>
@@ -8551,7 +8500,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="44" t="str">
         <v>Q_out</v>
       </c>
@@ -8571,7 +8520,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="44" t="str">
         <v>EC_flared</v>
       </c>
@@ -8591,7 +8540,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="44" t="str">
         <v>EF_flaredCH4</v>
       </c>
@@ -8611,7 +8560,7 @@
         <v>0.22889999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="44" t="str">
         <v>t</v>
       </c>
@@ -8631,8 +8580,8 @@
         <v>Unmanaged aerobic treatment</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="56" t="s">
         <v>119</v>
       </c>
@@ -8645,8 +8594,8 @@
         <v>t CH4</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="66" t="str" cm="1">
         <f t="array" ref="D32:E33">Common_Equations.Common_ConvertCH4ToCO2e_Arguments()</f>
         <v>ECH4</v>
@@ -8660,7 +8609,7 @@
         <v>4.7159433000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="66" t="str">
         <v>GWPCH4</v>
       </c>
@@ -8672,8 +8621,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="57" t="s">
         <v>120</v>
       </c>
@@ -8686,246 +8635,246 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="36" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="16"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="16"/>
     </row>
   </sheetData>
@@ -8944,7 +8893,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:J342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -8962,10 +8911,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -8981,13 +8930,13 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -8997,13 +8946,13 @@
         <v>Nitrous oxide emissions from flared biogas</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">Wastewater_N2O_Equations.VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas_Source()</f>
         <v>VEERG 2026: 11.1.3.1, Equation (1)</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
@@ -9012,18 +8961,18 @@
         <v>=Wastewater_N2O_Equations.VEERG_11_1_3_1__1_NitrousOxideEmissionsFromFlaredBiogas</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
         <v>Wastewater</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="27" t="s">
         <v>12</v>
       </c>
@@ -9032,7 +8981,7 @@
         <v>E_N2O</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="27" t="s">
         <v>4</v>
       </c>
@@ -9041,12 +8990,12 @@
         <v>t N2O</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
         <v>11.1.1-2 Wastewater CH4</v>
@@ -9071,7 +9020,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60" t="str">
         <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
         <v>11.1.3-4 Wastewater N2O</v>
@@ -9094,7 +9043,7 @@
         <v>3.7699999999999997E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="44" t="str">
         <v>EF_flaredN2O</v>
       </c>
@@ -9113,8 +9062,8 @@
         <v>1.132E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="s">
         <v>1</v>
       </c>
@@ -9130,13 +9079,13 @@
         <v>t N2O</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
         <v>Constants - Wastewater</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -9154,7 +9103,7 @@
         <v>4.26764E-7</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="66" t="str">
         <v>GWPN2O</v>
       </c>
@@ -9166,8 +9115,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="57" t="s">
         <v>120</v>
       </c>
@@ -9180,259 +9129,259 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="16"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="16"/>
     </row>
   </sheetData>
@@ -9451,7 +9400,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AI165"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -9478,13 +9427,13 @@
       <c r="AH1"/>
       <c r="AI1"/>
     </row>
-    <row r="2" spans="1:35" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="AG2"/>
       <c r="AH2"/>
       <c r="AI2"/>
     </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -9520,13 +9469,13 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -9536,19 +9485,19 @@
         <v>Methane correction factor for treatment facility type t used to treat wastewater</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">Wastewater_SourceData.Waste_MethaneCorrectionFactorWastewater_Source()</f>
         <v>VEERG 2026: Table A.4.1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="1" t="str" cm="1">
         <f t="array" ref="D7">Wastewater_SourceData.Waste_MethaneCorrectionFactorWastewater_Variable()</f>
         <v>CFww,t</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -9557,7 +9506,7 @@
         <v>fraction</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Wastewater'!A1", "Wastewater")</f>
         <v>Wastewater</v>
@@ -9569,7 +9518,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="24" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorWastewater_Data(), Table_SourceData_MCF_Wastewater[[#Headers],[Facility type t]], 0)</f>
         <v>Managed aerobic treatment</v>
@@ -9579,7 +9528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="24" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorWastewater_Data(), Table_SourceData_MCF_Wastewater[[#Headers],[Facility type t]], 0)</f>
         <v>Unmanaged aerobic treatment</v>
@@ -9589,7 +9538,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -9602,7 +9551,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'11.1.1-2 Wastewater CH4'!A1", "11.1.1-2 Wastewater CH4")</f>
         <v>11.1.1-2 Wastewater CH4</v>
@@ -9616,7 +9565,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="str">
         <f>HYPERLINK("#'11.1.3-4 Wastewater N2O'!A1", "11.1.3-4 Wastewater N2O")</f>
         <v>11.1.3-4 Wastewater N2O</v>
@@ -9630,9 +9579,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74" t="s">
         <v>1</v>
       </c>
@@ -9641,7 +9590,7 @@
         <v>Methane correction factor for treatment facility type t used to treat sludge</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="str">
         <f>HYPERLINK("#'Constants - Wastewater'!A1", "Constants - Wastewater")</f>
         <v>Constants - Wastewater</v>
@@ -9651,7 +9600,7 @@
         <v>VEERG 2026: Table A.4.1.4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -9661,13 +9610,13 @@
         <v>CFsludge,t</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="28" t="str" cm="1">
         <f t="array" ref="D20">Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Unit()</f>
         <v>fraction</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="24" t="s">
         <v>87</v>
       </c>
@@ -9675,7 +9624,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="24" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</f>
         <v>Managed aerobic treatment</v>
@@ -9685,7 +9634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="24" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</f>
         <v>Unmanaged aerobic treatment</v>
@@ -9695,7 +9644,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="24" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</f>
         <v>Anaerobic digestor/reactor</v>
@@ -9705,7 +9654,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="24" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</f>
         <v>Shallow anaerobic lagoon (≤ 2 m)</v>
@@ -9715,7 +9664,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="24" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Wastewater_SourceData.Waste_MethaneCorrectionFactorSludge_Data(), Table_SourceData_MCF_Sludge[[#Headers],[Facility type t]], 0)</f>
         <v>Deep anaerobic lagoon (&gt; 2m)</v>
@@ -9725,21 +9674,21 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="5" t="str" cm="1">
         <f t="array" ref="D29">Wastewater_SourceData.Waste_MethaneEmissionFactorWastewater_Title()</f>
         <v>Methane emission factor for wastewater</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="4" t="str" cm="1">
         <f t="array" ref="D30">Wastewater_SourceData.Waste_MethaneEmissionFactorWastewater_Source()</f>
         <v>VEERG 2026: 11.2.3 Constants</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="27" t="str" cm="1">
         <f t="array" ref="D31">Wastewater_SourceData.Waste_MethaneEmissionFactorWastewater_Variable()</f>
         <v>EFww</v>
@@ -9753,21 +9702,21 @@
         <v>kg CH4 / kg COD</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="5" t="str" cm="1">
         <f t="array" ref="D34">Wastewater_SourceData.Waste_MethaneEmissionFactorSludge_Title()</f>
         <v>Methane emission factor for sludge</v>
       </c>
     </row>
-    <row r="35" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="4" t="str" cm="1">
         <f t="array" ref="D35">Wastewater_SourceData.Waste_MethaneEmissionFactorSludge_Source()</f>
         <v>VEERG 2026: 11.2.3 Constants</v>
       </c>
     </row>
-    <row r="36" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="27" t="str" cm="1">
         <f t="array" ref="D36">Wastewater_SourceData.Waste_MethaneEmissionFactorSludge_Variable()</f>
         <v>EFsludge</v>
@@ -9781,21 +9730,21 @@
         <v>kg CH4 / kg COD</v>
       </c>
     </row>
-    <row r="37" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="5" t="str" cm="1">
         <f t="array" ref="D39">Wastewater_SourceData.Waste_EnergyContentFactorSludgeBiogasFlared_Title()</f>
         <v>Energy content factor of sludge biogas flared</v>
       </c>
     </row>
-    <row r="40" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="4" t="str" cm="1">
         <f t="array" ref="D40">Wastewater_SourceData.Waste_EnergyContentFactorSludgeBiogasFlared_Source()</f>
         <v>VEERG 2026: 11.2.3 Constants</v>
       </c>
     </row>
-    <row r="41" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="27" t="str" cm="1">
         <f t="array" ref="D41">Wastewater_SourceData.Waste_EnergyContentFactorSludgeBiogasFlared_Variable()</f>
         <v>ECflared</v>
@@ -9809,21 +9758,21 @@
         <v>GJ / m3</v>
       </c>
     </row>
-    <row r="42" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="5" t="str" cm="1">
         <f t="array" ref="D44">Wastewater_SourceData.Waste_MethaneEmissionFactorSludgeBiogasFlared_Title()</f>
         <v>Methane emission factor for sludge biogas flared</v>
       </c>
     </row>
-    <row r="45" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="4" t="str" cm="1">
         <f t="array" ref="D45">Wastewater_SourceData.Waste_MethaneEmissionFactorSludgeBiogasFlared_Source()</f>
         <v>VEERG 2026: 11.2.3 Constants</v>
       </c>
     </row>
-    <row r="46" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="27" t="str" cm="1">
         <f t="array" ref="D46">Wastewater_SourceData.Waste_MethaneEmissionFactorSludgeBiogasFlared_Variable()</f>
         <v>EFflared,CH4</v>
@@ -9837,21 +9786,21 @@
         <v>kg CH4 / GJ</v>
       </c>
     </row>
-    <row r="47" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="5" t="str" cm="1">
         <f t="array" ref="D49">Wastewater_SourceData.Waste_NitrousOxideEmissionFactorSludgeBiogasFlared_Title()</f>
         <v>Nitrous oxide emission factor for sludge biogas flared</v>
       </c>
     </row>
-    <row r="50" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="4" t="str" cm="1">
         <f t="array" ref="D50">Wastewater_SourceData.Waste_NitrousOxideEmissionFactorSludgeBiogasFlared_Source()</f>
         <v>VEERG 2026: 11.2.3 Constants</v>
       </c>
     </row>
-    <row r="51" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="27" t="str" cm="1">
         <f t="array" ref="D51">Wastewater_SourceData.Waste_NitrousOxideEmissionFactorSludgeBiogasFlared_Variable()</f>
         <v>EFflared,N2O</v>
@@ -9865,120 +9814,120 @@
         <v>kg N2O / GJ</v>
       </c>
     </row>
-    <row r="52" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:6" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9996,7 +9945,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="6" customWidth="1"/>
@@ -10029,10 +9978,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -10059,11 +10008,11 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="2"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -10071,7 +10020,7 @@
       </c>
       <c r="BM5" s="2"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="74" t="s">
         <v>1</v>
       </c>
@@ -10085,7 +10034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="53" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -10103,7 +10052,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -10121,7 +10070,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="24" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10136,7 +10085,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="24" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10151,7 +10100,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="24" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10167,7 +10116,7 @@
       </c>
       <c r="BM11" s="2"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="24" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10183,7 +10132,7 @@
       </c>
       <c r="BM12" s="2"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="24" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10198,7 +10147,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="24" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -10213,129 +10162,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="5" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="4" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="24" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="24" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="24" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="24" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="24" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="24" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="24" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="24" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="24" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="24" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="5" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="4" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="24" t="s">
         <v>10</v>
@@ -10344,7 +10293,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="24" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10355,7 +10304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="24" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10366,7 +10315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="24" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10377,7 +10326,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="24" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10388,7 +10337,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="24" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10399,7 +10348,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="24" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10410,7 +10359,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="24" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -10421,24 +10370,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="5" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="4" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="24" t="s">
         <v>10</v>
@@ -10456,7 +10405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="24" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10479,7 +10428,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="24" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10502,7 +10451,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="24" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10525,7 +10474,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="24" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10548,7 +10497,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="24" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10571,7 +10520,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="24" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10594,7 +10543,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="24" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -10617,49 +10566,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="5" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="4" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="29" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="29" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="29" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="24" t="s">
         <v>3</v>
@@ -10668,7 +10617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="24" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10679,7 +10628,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="24" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10690,7 +10639,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="24" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10701,7 +10650,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="24" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10712,7 +10661,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="24" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10723,7 +10672,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="24" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10734,7 +10683,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="24" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10745,7 +10694,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="24" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10756,7 +10705,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="24" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10767,7 +10716,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="24" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10778,7 +10727,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="24" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10789,7 +10738,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="24" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10800,7 +10749,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="24" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10811,7 +10760,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="24" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -10822,64 +10771,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="5" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="4" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="29" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="29" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="29" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="29" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="29" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="24" t="s">
         <v>3</v>
@@ -10931,7 +10880,7 @@
       </c>
       <c r="T89" s="24"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="24" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -10999,7 +10948,7 @@
       </c>
       <c r="T90" s="24"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="24" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11067,7 +11016,7 @@
       </c>
       <c r="T91" s="24"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="24" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11135,7 +11084,7 @@
       </c>
       <c r="T92" s="24"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="24" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11203,7 +11152,7 @@
       </c>
       <c r="T93" s="24"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="24" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11271,7 +11220,7 @@
       </c>
       <c r="T94" s="24"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="24" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11339,7 +11288,7 @@
       </c>
       <c r="T95" s="24"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="24" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11407,7 +11356,7 @@
       </c>
       <c r="T96" s="24"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="24" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -11475,66 +11424,66 @@
       </c>
       <c r="T97" s="24"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="28" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="28" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="28" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="28" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="28"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="5" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="4" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="29" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="24" t="s">
         <v>35</v>
@@ -11549,7 +11498,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="24" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -11568,7 +11517,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="24" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -11587,7 +11536,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="24" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -11606,13 +11555,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="5" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -11620,7 +11569,7 @@
       </c>
       <c r="BN115" s="6"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="4" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -11628,7 +11577,7 @@
       </c>
       <c r="BN116" s="6"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="29" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -11636,11 +11585,11 @@
       </c>
       <c r="BN117" s="6"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="6"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="24" t="s">
         <v>38</v>
@@ -11656,7 +11605,7 @@
       </c>
       <c r="BN119" s="6"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="24" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -11676,7 +11625,7 @@
       </c>
       <c r="BN120" s="6"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="24" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -11696,31 +11645,31 @@
       </c>
       <c r="BN121" s="6"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="6"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="5" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="4" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="24" t="s">
         <v>40</v>
@@ -11729,7 +11678,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="24" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -11740,7 +11689,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="24" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -11751,13 +11700,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="5" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -11765,7 +11714,7 @@
       </c>
       <c r="E132" s="16"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="4" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -11773,7 +11722,7 @@
       </c>
       <c r="E133" s="16"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>46</v>
@@ -11782,7 +11731,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -11793,7 +11742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -11804,10 +11753,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="6"/>
       <c r="BO138" s="6"/>
@@ -11822,7 +11771,7 @@
       <c r="BX138" s="6"/>
       <c r="BY138" s="6"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="5" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -11841,7 +11790,7 @@
       <c r="BX139" s="6"/>
       <c r="BY139" s="6"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="4" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -11860,7 +11809,7 @@
       <c r="BX140" s="6"/>
       <c r="BY140" s="6"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="29" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -11868,7 +11817,7 @@
       </c>
       <c r="BN141" s="6"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="24" t="s">
         <v>56</v>
@@ -11878,7 +11827,7 @@
       </c>
       <c r="BN142" s="6"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="24" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -11890,7 +11839,7 @@
       </c>
       <c r="BN143" s="6"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -11902,7 +11851,7 @@
       </c>
       <c r="BN144" s="6"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -11914,7 +11863,7 @@
       </c>
       <c r="BN145" s="6"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -11926,7 +11875,7 @@
       </c>
       <c r="BN146" s="6"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -11938,15 +11887,15 @@
       </c>
       <c r="BN147" s="6"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="6"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="6"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="5" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -11954,7 +11903,7 @@
       </c>
       <c r="BN150" s="6"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="4" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -11962,11 +11911,11 @@
       </c>
       <c r="BN151" s="6"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="6"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="24" t="s">
         <v>42</v>
@@ -11986,7 +11935,7 @@
       <c r="BL153" s="2"/>
       <c r="BM153" s="2"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="24" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12008,7 +11957,7 @@
       <c r="BL154" s="2"/>
       <c r="BM154" s="2"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="24" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12030,7 +11979,7 @@
       <c r="BL155" s="2"/>
       <c r="BM155" s="2"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="24" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12041,7 +11990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="24" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12052,7 +12001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="24" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -12063,34 +12012,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="5" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="16"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="4" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="16"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="16"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="16" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -12099,17 +12048,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="6"/>
       <c r="BO165" s="6"/>
       <c r="BP165" s="6"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="6"/>
       <c r="BO166" s="6"/>
       <c r="BP166" s="6"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="5" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -12118,7 +12067,7 @@
       <c r="BO167" s="6"/>
       <c r="BP167" s="6"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="4" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -12127,7 +12076,7 @@
       <c r="BO168" s="6"/>
       <c r="BP168" s="6"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="4" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -12136,7 +12085,7 @@
       <c r="BO169" s="6"/>
       <c r="BP169" s="6"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -12148,17 +12097,17 @@
       <c r="BO170" s="6"/>
       <c r="BP170" s="6"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="6"/>
       <c r="BO171" s="6"/>
       <c r="BP171" s="6"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="6"/>
       <c r="BO172" s="6"/>
       <c r="BP172" s="6"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="5" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -12167,7 +12116,7 @@
       <c r="BO173" s="6"/>
       <c r="BP173" s="6"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="4" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -12176,7 +12125,7 @@
       <c r="BO174" s="6"/>
       <c r="BP174" s="6"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -12189,17 +12138,17 @@
       <c r="BO175" s="6"/>
       <c r="BP175" s="6"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="6"/>
       <c r="BO176" s="6"/>
       <c r="BP176" s="6"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="6"/>
       <c r="BO177" s="6"/>
       <c r="BP177" s="6"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="5" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -12208,7 +12157,7 @@
       <c r="BO178" s="6"/>
       <c r="BP178" s="6"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="4" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -12217,39 +12166,39 @@
       <c r="BO179" s="6"/>
       <c r="BP179" s="6"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="28" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="29" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="29" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="29" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="29" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="29" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="24" t="s">
         <v>50</v>
       </c>
@@ -12266,7 +12215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="24" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -12288,7 +12237,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="24" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -12310,7 +12259,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="24" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -12332,7 +12281,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="24" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -12354,7 +12303,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="24" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -12376,7 +12325,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="24" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -12398,7 +12347,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="24" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -12420,7 +12369,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="24" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -12442,7 +12391,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="24" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -12464,7 +12413,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="24" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -12486,7 +12435,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="24" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -12508,7 +12457,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="24" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -12530,7 +12479,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="24" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -12552,31 +12501,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="5" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="4" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="29" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="28" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="24" t="s">
         <v>3</v>
       </c>
@@ -12584,7 +12533,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="24" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -12594,7 +12543,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -12604,13 +12553,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="24" t="s">
         <v>55</v>
       </c>
@@ -12618,7 +12567,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="24" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -12628,7 +12577,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -12638,7 +12587,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -12648,7 +12597,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -12658,7 +12607,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -12668,7 +12617,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -12678,7 +12627,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -12688,7 +12637,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -12698,7 +12647,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -12708,7 +12657,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -12718,7 +12667,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -12728,7 +12677,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -12738,25 +12687,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="5" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="4" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="29" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="24" t="s">
         <v>34</v>
       </c>
@@ -12806,7 +12755,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="24" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -12872,7 +12821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -12938,7 +12887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13004,7 +12953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13070,7 +13019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -13136,7 +13085,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13202,7 +13151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13268,7 +13217,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13334,7 +13283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13400,7 +13349,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13466,7 +13415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13532,7 +13481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13598,7 +13547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13664,7 +13613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13730,7 +13679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13796,7 +13745,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -13862,7 +13811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -13928,7 +13877,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -13994,7 +13943,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -14060,31 +14009,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="5" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="4" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="28" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="24" t="s">
         <v>77</v>
       </c>
@@ -14092,7 +14041,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="24" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -14102,7 +14051,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -14112,17 +14061,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="24" t="s">
         <v>134</v>
       </c>
@@ -14133,7 +14082,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="24" t="s">
         <v>137</v>
       </c>
@@ -14144,7 +14093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="24" t="s">
         <v>139</v>
       </c>
@@ -14155,7 +14104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="24" t="s">
         <v>141</v>
       </c>
@@ -14166,7 +14115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="24" t="s">
         <v>143</v>
       </c>
@@ -14177,7 +14126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="24" t="s">
         <v>145</v>
       </c>
@@ -14188,12 +14137,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="24" t="s">
         <v>134</v>
       </c>
@@ -14204,7 +14153,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="24" t="s">
         <v>148</v>
       </c>
@@ -14215,7 +14164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="24" t="s">
         <v>150</v>
       </c>
@@ -14226,7 +14175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="24" t="s">
         <v>152</v>
       </c>
@@ -14237,7 +14186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="24" t="s">
         <v>154</v>
       </c>
@@ -14248,7 +14197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="24" t="s">
         <v>156</v>
       </c>
@@ -14259,12 +14208,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="24" t="s">
         <v>134</v>
       </c>
@@ -14275,7 +14224,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="24" t="s">
         <v>159</v>
       </c>
@@ -14286,7 +14235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="24" t="s">
         <v>161</v>
       </c>
@@ -14297,7 +14246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="24" t="s">
         <v>163</v>
       </c>
@@ -14308,7 +14257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="24" t="s">
         <v>165</v>
       </c>
@@ -14319,7 +14268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="24" t="s">
         <v>167</v>
       </c>
@@ -14330,12 +14279,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="24" t="s">
         <v>134</v>
       </c>
@@ -14346,7 +14295,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="24" t="s">
         <v>170</v>
       </c>
@@ -14357,7 +14306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="24" t="s">
         <v>172</v>
       </c>
@@ -14368,7 +14317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="24" t="s">
         <v>174</v>
       </c>
@@ -14379,7 +14328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="24" t="s">
         <v>176</v>
       </c>
@@ -14390,7 +14339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="24" t="s">
         <v>178</v>
       </c>
